--- a/results_minsup_ESBL/minsup_0_001/rep3/tab_recap_itemsets_0.95.xlsx
+++ b/results_minsup_ESBL/minsup_0_001/rep3/tab_recap_itemsets_0.95.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">dataset</t>
   </si>
@@ -38,7 +38,31 @@
     <t xml:space="preserve">2018_BLSE</t>
   </si>
   <si>
+    <t xml:space="preserve">2019_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021_BLSE</t>
+  </si>
+  <si>
     <t xml:space="preserve">2022_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018_non_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019_non_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020_non_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021_non_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022_non_BLSE</t>
   </si>
 </sst>
 </file>
@@ -418,22 +442,206 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>700834</v>
+        <v>611675</v>
       </c>
       <c r="C3" t="n">
-        <v>4833</v>
+        <v>5374</v>
       </c>
       <c r="D3" t="n">
-        <v>6.44</v>
+        <v>6.19</v>
       </c>
       <c r="E3" t="n">
         <v>11</v>
       </c>
       <c r="F3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>548904</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5681</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="n">
+        <v>697177</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4745</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="n">
+        <v>700834</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4866</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" t="n">
         <v>4.12</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G6" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2527</v>
+      </c>
+      <c r="C7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3974</v>
+      </c>
+      <c r="C8" t="n">
+        <v>82</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3828</v>
+      </c>
+      <c r="C9" t="n">
+        <v>75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4965</v>
+      </c>
+      <c r="C10" t="n">
+        <v>89</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4448</v>
+      </c>
+      <c r="C11" t="n">
+        <v>93</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
